--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_257_R26.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_257_R26.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5938</v>
+        <v>4.0149</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6498</v>
+        <v>5.0036</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.056</v>
+        <v>-0.9888</v>
       </c>
       <c r="G2" t="n">
         <v>3.4896</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2722</v>
+        <v>-0.8511</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.963</v>
+        <v>-0.6091</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3093</v>
+        <v>-0.242</v>
       </c>
       <c r="V2" t="n">
         <v>1.6083</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.641</v>
+        <v>2.9784</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9015</v>
+        <v>3.3733</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2605</v>
+        <v>-0.3949</v>
       </c>
       <c r="G3" t="n">
         <v>3.8986</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8839</v>
+        <v>-0.5465</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.187</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3031</v>
+        <v>0.1687</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1418</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. HOARD</t>
+          <t>T. LEAF</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4371</v>
+        <v>1.2092</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2951</v>
+        <v>1.8536</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.858</v>
+        <v>-0.6444</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.4983</v>
+        <v>2.9597</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7791</v>
+        <v>1.8019</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7193000000000001</v>
+        <v>1.1578</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2501</v>
+        <v>3.4496</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4404</v>
+        <v>2.2351</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8097</v>
+        <v>1.2146</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.7484</v>
+        <v>-0.4899</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2195</v>
+        <v>-0.4331</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.529</v>
+        <v>-0.0568</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6133</v>
+        <v>-0.9102</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0272</v>
+        <v>-0.4362</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6405</v>
+        <v>-0.474</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9304</v>
+        <v>-1.0722</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. LEAF</t>
+          <t>J. HOARD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.175</v>
+        <v>0.8651</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6177</v>
+        <v>2.0592</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4428</v>
+        <v>-1.1941</v>
       </c>
       <c r="G5" t="n">
-        <v>2.9597</v>
+        <v>-1.4983</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8019</v>
+        <v>-0.7791</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1578</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4496</v>
+        <v>1.2501</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2351</v>
+        <v>0.4404</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2146</v>
+        <v>0.8097</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4899</v>
+        <v>-2.7484</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4331</v>
+        <v>-1.2195</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0568</v>
+        <v>-1.529</v>
       </c>
       <c r="P5" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9445</v>
+        <v>0.0413</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6721</v>
+        <v>-0.2631</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2724</v>
+        <v>0.3044</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0722</v>
+        <v>0.9304</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6232</v>
+        <v>0.8084</v>
       </c>
       <c r="E6" t="n">
-        <v>1.283</v>
+        <v>1.4009</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6597</v>
+        <v>-0.5925</v>
       </c>
       <c r="G6" t="n">
         <v>1.1249</v>
@@ -922,13 +922,13 @@
         <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7336</v>
+        <v>-0.5485</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1494</v>
+        <v>-0.0314</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5843</v>
+        <v>-0.5171</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SANTOS</t>
+          <t>W. RAYMAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1044</v>
+        <v>-0.0791</v>
       </c>
       <c r="E7" t="n">
-        <v>1.708</v>
+        <v>0.4213</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8124</v>
+        <v>-0.5004</v>
       </c>
       <c r="G7" t="n">
-        <v>2.18</v>
+        <v>-0.4506</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2832</v>
+        <v>-0.1763</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8968</v>
+        <v>-0.2743</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7661</v>
+        <v>0.7003</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2337</v>
+        <v>0.2353</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5324</v>
+        <v>0.465</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5861</v>
+        <v>-1.1509</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0495</v>
+        <v>-0.4116</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6581</v>
+        <v>-0.4118</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0474</v>
+        <v>-0.279</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7055</v>
+        <v>-0.1329</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9304</v>
+        <v>-1.0722</v>
       </c>
       <c r="W7" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W. RAYMAN</t>
+          <t>M. SANTOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.483</v>
+        <v>-0.1894</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1854</v>
+        <v>1.3542</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6684</v>
+        <v>-1.5435</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4506</v>
+        <v>2.18</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1763</v>
+        <v>1.2832</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2743</v>
+        <v>0.8968</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7003</v>
+        <v>2.7661</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2353</v>
+        <v>1.2337</v>
       </c>
       <c r="L8" t="n">
-        <v>0.465</v>
+        <v>1.5324</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1509</v>
+        <v>-0.5861</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4116</v>
+        <v>0.0495</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8556</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8158</v>
+        <v>-0.7431</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5149</v>
+        <v>-0.3064</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3009</v>
+        <v>-0.4367</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0722</v>
+        <v>-0.9304</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.581</v>
+        <v>-2.4124</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8416</v>
+        <v>-2.6057</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2606</v>
+        <v>0.1934</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6673</v>
@@ -1156,13 +1156,13 @@
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9137</v>
+        <v>-0.7451</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6721</v>
+        <v>-0.4362</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2416</v>
+        <v>-0.3088</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7956</v>
+        <v>-3.4869</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8300999999999999</v>
+        <v>-1.6558</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9655</v>
+        <v>-1.8311</v>
       </c>
       <c r="G10" t="n">
         <v>-3.118</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.036</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6018</v>
+        <v>-0.2238</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6379</v>
+        <v>-0.5034</v>
       </c>
       <c r="V10" t="n">
         <v>1.7501</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8069</v>
+        <v>-4.0092</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4729</v>
+        <v>-0.7088</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.334</v>
+        <v>-3.3004</v>
       </c>
       <c r="G11" t="n">
         <v>-3.3064</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1937</v>
+        <v>-0.396</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0395</v>
+        <v>-0.1964</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2333</v>
+        <v>-0.1997</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4665</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3008000000000006</v>
+        <v>-0.3010000000000006</v>
       </c>
       <c r="E12" t="n">
-        <v>10.4959</v>
+        <v>10.4958</v>
       </c>
       <c r="F12" t="n">
         <v>-10.7967</v>
       </c>
       <c r="G12" t="n">
-        <v>3.612199999999998</v>
+        <v>3.6122</v>
       </c>
       <c r="H12" t="n">
         <v>5.7199</v>
@@ -1390,13 +1390,13 @@
         <v>13.9173</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.838199999999999</v>
+        <v>-5.838299999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.497</v>
+        <v>-3.4968</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.3416</v>
+        <v>-2.3415</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3943000000000001</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>D. OSETKOWSKI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.469</v>
+        <v>3.6878</v>
       </c>
       <c r="E13" t="n">
-        <v>7.6839</v>
+        <v>4.971</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.2149</v>
+        <v>-1.2833</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4719</v>
+        <v>2.6073</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4655</v>
+        <v>-1.7525</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9936</v>
+        <v>4.3598</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9166</v>
+        <v>5.6101</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6958</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2208</v>
+        <v>5.1024</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.4447</v>
+        <v>-3.0027</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2303</v>
+        <v>-2.2601</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.2144</v>
+        <v>-0.7426</v>
       </c>
       <c r="P13" t="n">
         <v>0.9278</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9275</v>
+        <v>0.8305</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4812</v>
+        <v>-0.0154</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4463</v>
+        <v>0.8459</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1418</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>2.2862</v>
+        <v>0.5361</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1444</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. OSETKOWSKI</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5298</v>
+        <v>2.7898</v>
       </c>
       <c r="E14" t="n">
-        <v>4.7351</v>
+        <v>5.9147</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.2053</v>
+        <v>-3.1249</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6073</v>
+        <v>0.4719</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.7525</v>
+        <v>1.4655</v>
       </c>
       <c r="I14" t="n">
-        <v>4.3598</v>
+        <v>-0.9936</v>
       </c>
       <c r="J14" t="n">
-        <v>5.6101</v>
+        <v>2.9166</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5076000000000001</v>
+        <v>2.6958</v>
       </c>
       <c r="L14" t="n">
-        <v>5.1024</v>
+        <v>0.2208</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.0027</v>
+        <v>-2.4447</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.2601</v>
+        <v>-1.2303</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7426</v>
+        <v>-1.2144</v>
       </c>
       <c r="P14" t="n">
         <v>0.9278</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6726</v>
+        <v>1.2483</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2513</v>
+        <v>0.7119</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9239000000000001</v>
+        <v>0.5364</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0.1418</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5361</v>
+        <v>2.2862</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.214</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3907</v>
+        <v>0.2213</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7002</v>
+        <v>1.2284</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3095</v>
+        <v>-1.007</v>
       </c>
       <c r="G15" t="n">
         <v>-0.7036</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8623</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9752</v>
+        <v>0.5034</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1129</v>
+        <v>0.1896</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. LAKIC</t>
+          <t>I. BONGA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3045</v>
+        <v>0.007</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3407</v>
+        <v>1.8263</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6453</v>
+        <v>-1.8194</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.8306</v>
+        <v>-0.4037</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7933</v>
+        <v>2.8486</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.0373</v>
+        <v>-3.2523</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1469</v>
+        <v>2.8098</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1008</v>
+        <v>5.1087</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.2477</v>
+        <v>-2.2989</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6838</v>
+        <v>-3.2135</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8942</v>
+        <v>-2.2601</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7896</v>
+        <v>-0.9534</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8303</v>
+        <v>1.0163</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4876</v>
+        <v>0.2638</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3427</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. RADANOV</t>
+          <t>A. LAKIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4635</v>
+        <v>-0.4389</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3305</v>
+        <v>0.3407</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1331</v>
+        <v>-0.7796999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.1309</v>
+        <v>-1.8306</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8666</v>
+        <v>-0.7933</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2643</v>
+        <v>-1.0373</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6687</v>
+        <v>-0.1469</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6687</v>
+        <v>0.1008</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.2477</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4622</v>
+        <v>-1.6838</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1979</v>
+        <v>-0.8942</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2643</v>
+        <v>-0.7896</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1133</v>
+        <v>0.6959</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3383</v>
+        <v>0.4876</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2249</v>
+        <v>0.2082</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. BONGA</t>
+          <t>A. RADANOV</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.447</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2366</v>
+        <v>-0.4484</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9094</v>
+        <v>0.0014</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4037</v>
+        <v>-2.1309</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8486</v>
+        <v>-1.8666</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.2523</v>
+        <v>-0.2643</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8098</v>
+        <v>-0.6687</v>
       </c>
       <c r="K18" t="n">
-        <v>5.1087</v>
+        <v>-0.6687</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.2989</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.2135</v>
+        <v>-1.4622</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.2601</v>
+        <v>-1.1979</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9534</v>
+        <v>-0.2643</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3365</v>
+        <v>0.1298</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.326</v>
+        <v>0.2203</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6625</v>
+        <v>-0.0905</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1418</v>
+        <v>0.3943</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.214</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6896</v>
+        <v>-0.7905</v>
       </c>
       <c r="E19" t="n">
         <v>0.6481</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3378</v>
+        <v>-1.4386</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8544</v>
@@ -1936,13 +1936,13 @@
         <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6286</v>
+        <v>0.5278</v>
       </c>
       <c r="T19" t="n">
         <v>0.2636</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3651</v>
+        <v>0.2642</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7445</v>
+        <v>-1.8795</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9291</v>
+        <v>-2.2214</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1846</v>
+        <v>0.3419</v>
       </c>
       <c r="G20" t="n">
         <v>-2.4787</v>
@@ -2014,13 +2014,13 @@
         <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2478</v>
+        <v>0.6172</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7389</v>
+        <v>-0.0312</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4911</v>
+        <v>0.6484</v>
       </c>
       <c r="V20" t="n">
         <v>0.6778999999999999</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2136</v>
+        <v>-2.0627</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2883</v>
+        <v>-1.4627</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9253</v>
+        <v>-0.6</v>
       </c>
       <c r="G21" t="n">
         <v>1.7105</v>
@@ -2092,13 +2092,13 @@
         <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2851</v>
+        <v>0.8659</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8883</v>
+        <v>-0.0626</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6032</v>
+        <v>0.9285</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3009000000000008</v>
+        <v>1.087300000000001</v>
       </c>
       <c r="E22" t="n">
         <v>10.7967</v>
       </c>
       <c r="F22" t="n">
-        <v>-10.496</v>
+        <v>-9.7096</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.612200000000001</v>
+        <v>-3.6122</v>
       </c>
       <c r="H22" t="n">
-        <v>-5.720000000000001</v>
+        <v>-5.72</v>
       </c>
       <c r="I22" t="n">
         <v>2.1078</v>
@@ -2149,7 +2149,7 @@
         <v>8.2629</v>
       </c>
       <c r="L22" t="n">
-        <v>7.928699999999999</v>
+        <v>7.9287</v>
       </c>
       <c r="M22" t="n">
         <v>-19.804</v>
@@ -2170,16 +2170,16 @@
         <v>11.5978</v>
       </c>
       <c r="S22" t="n">
-        <v>5.838200000000001</v>
+        <v>6.6247</v>
       </c>
       <c r="T22" t="n">
-        <v>2.341399999999999</v>
+        <v>2.3414</v>
       </c>
       <c r="U22" t="n">
-        <v>3.497</v>
+        <v>4.2832</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3943</v>
+        <v>0.3943000000000001</v>
       </c>
       <c r="W22" t="n">
         <v>6.1807</v>
